--- a/漢字（かんじ）/chi.xlsx
+++ b/漢字（かんじ）/chi.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="88">
   <si>
     <t>仮名</t>
   </si>
@@ -53,7 +53,8 @@
 地理｜ちり
 団地｜だんち
 盆地｜ぼんち
-大地｜だいち</t>
+大地｜だいち
+境地｜きょうち</t>
   </si>
   <si>
     <t>ちつ</t>
@@ -70,6 +71,24 @@
   </si>
   <si>
     <t>経験値｜けいけんち</t>
+  </si>
+  <si>
+    <t>ちか</t>
+  </si>
+  <si>
+    <t>近</t>
+  </si>
+  <si>
+    <t>近道｜ちかみち</t>
+  </si>
+  <si>
+    <t>置</t>
+  </si>
+  <si>
+    <t>配置｜はいち
+設置｜せっち
+装置｜そうち
+録画装置｜ろくがそうち</t>
   </si>
   <si>
     <t>ちゃく</t>
@@ -88,13 +107,11 @@
 沈着冷静｜ちんちゃくれいせい</t>
   </si>
   <si>
-    <t>置</t>
-  </si>
-  <si>
-    <t>配置｜はいち
-設置｜せっち
-装置｜そうち
-録画装置｜ろくがそうち</t>
+    <t>池</t>
+  </si>
+  <si>
+    <t>電池｜でんち
+太陽電池｜たいようでんち</t>
   </si>
   <si>
     <t>ちょう</t>
@@ -111,11 +128,11 @@
 直系血族｜ちょっけいけつぞく</t>
   </si>
   <si>
-    <t>池</t>
-  </si>
-  <si>
-    <t>電池｜でんち
-太陽電池｜たいようでんち</t>
+    <t>遅</t>
+  </si>
+  <si>
+    <t>遅刻｜ちこく
+遅刻早退｜ちこくそうたい</t>
   </si>
   <si>
     <t>ちゃ</t>
@@ -126,19 +143,6 @@
   <si>
     <t>紅茶｜こうちゃ
 緑茶｜りょくちゃ</t>
-  </si>
-  <si>
-    <t>遅</t>
-  </si>
-  <si>
-    <t>遅刻｜ちこく
-遅刻早退｜ちこくそうたい</t>
-  </si>
-  <si>
-    <t>ちまた</t>
-  </si>
-  <si>
-    <t>巷</t>
   </si>
   <si>
     <t>知</t>
@@ -151,6 +155,21 @@
 知識｜ちしき</t>
   </si>
   <si>
+    <t>ちまた</t>
+  </si>
+  <si>
+    <t>巷</t>
+  </si>
+  <si>
+    <t>ちん</t>
+  </si>
+  <si>
+    <t>致</t>
+  </si>
+  <si>
+    <t>一致｜いっち</t>
+  </si>
+  <si>
     <t>ちち</t>
   </si>
   <si>
@@ -158,15 +177,6 @@
   </si>
   <si>
     <t>父親｜ちちおや</t>
-  </si>
-  <si>
-    <t>ちん</t>
-  </si>
-  <si>
-    <t>致</t>
-  </si>
-  <si>
-    <t>一致｜いっち</t>
   </si>
   <si>
     <t>沈</t>
@@ -353,7 +363,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,13 +382,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -828,148 +831,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1305,7 +1308,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="29.8888888888889" customWidth="1"/>
@@ -1352,7 +1355,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="144" spans="1:7">
+    <row r="3" ht="18" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1362,7 +1365,7 @@
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1372,7 +1375,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="108" spans="1:7">
+    <row r="4" ht="144" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1385,14 +1388,14 @@
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="36" spans="1:7">
+    <row r="5" ht="108" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1405,7 +1408,7 @@
       <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -1428,28 +1431,28 @@
       <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="G6" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="7" ht="90" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="41.4" customHeight="1" spans="1:7">
+    <row r="8" ht="18" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
@@ -1459,266 +1462,276 @@
       <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" ht="36" spans="1:7">
+      <c r="E8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="41.4" customHeight="1" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" ht="36" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" ht="22.2" customHeight="1" spans="1:7">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" ht="18" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" ht="94.8" customHeight="1" spans="1:7">
-      <c r="A14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" ht="22.2" customHeight="1"/>
+    <row r="15" ht="94.8" customHeight="1" spans="1:7">
+      <c r="A15" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" ht="17.4" customHeight="1" spans="1:7">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" ht="19.8" customHeight="1" spans="1:7">
+      <c r="C15" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" ht="17.4" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" ht="18" spans="1:3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" ht="19.8" customHeight="1" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" ht="36" spans="1:3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" ht="18" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" t="s">
-        <v>57</v>
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" ht="18" spans="1:3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" ht="36" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" ht="90" spans="1:3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" ht="18" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" ht="36" spans="1:3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" ht="90" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" ht="36" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" ht="18" spans="1:3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" ht="36" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="25" ht="41.4" spans="1:3">
+      <c r="C24" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" ht="18" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="26" ht="126" spans="1:3">
+      <c r="C25" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" ht="41.4" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="27" ht="36" spans="1:3">
+      <c r="C26" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" ht="126" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" ht="36" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
+        <v>21</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" ht="36" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" ht="36" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" ht="18" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>16</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" ht="36" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="32" ht="46.8" spans="1:3">
-      <c r="A32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="5" t="s">
+    </row>
+    <row r="32" ht="18" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>84</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" ht="46.8" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/chi.xlsx
+++ b/漢字（かんじ）/chi.xlsx
@@ -227,6 +227,8 @@
 中旬｜ちゅうじゅん
 中毒｜ちゅうどく
 中型｜ちゅうがた
+中間｜ちゅうかん
+中間報告｜ちゅうかんほうこく
 最中｜さいちゅう</t>
   </si>
   <si>

--- a/漢字（かんじ）/chi.xlsx
+++ b/漢字（かんじ）/chi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="ち" sheetId="1" r:id="rId1"/>
@@ -1310,7 +1310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="29.8888888888889" customWidth="1"/>
@@ -1526,38 +1526,48 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" ht="22.2" customHeight="1"/>
-    <row r="15" ht="94.8" customHeight="1" spans="1:7">
+    <row r="14" ht="94.8" customHeight="1" spans="1:7">
+      <c r="A14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" ht="17.4" customHeight="1" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" ht="17.4" customHeight="1" spans="1:7">
+        <v>52</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" ht="19.8" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" ht="19.8" customHeight="1" spans="1:3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:3">
@@ -1565,54 +1575,54 @@
         <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" ht="18" spans="1:3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" ht="36" spans="1:3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" ht="18" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>60</v>
+      <c r="B20" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" ht="18" spans="1:3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" ht="90" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" ht="90" spans="1:3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" ht="36" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="36" spans="1:3">
@@ -1620,76 +1630,76 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" ht="36" spans="1:3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" ht="18" spans="1:3">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" ht="18" spans="1:3">
+        <v>70</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" ht="41.4" spans="1:3">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" ht="41.4" spans="1:3">
+        <v>72</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" ht="126" spans="1:3">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" ht="126" spans="1:3">
+        <v>74</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" ht="36" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" ht="36" spans="1:3">
       <c r="A28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>76</v>
+      <c r="B28" t="s">
+        <v>78</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" ht="36" spans="1:3">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B29" t="s">
-        <v>78</v>
+      <c r="B29" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" ht="36" spans="1:3">
@@ -1697,42 +1707,31 @@
         <v>21</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" ht="36" spans="1:3">
-      <c r="A31" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" ht="18" spans="1:3">
+      <c r="A31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" ht="18" spans="1:3">
-      <c r="A32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" ht="46.8" spans="1:3">
+      <c r="A32" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" ht="46.8" spans="1:3">
-      <c r="A33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>87</v>
       </c>
     </row>

--- a/漢字（かんじ）/chi.xlsx
+++ b/漢字（かんじ）/chi.xlsx
@@ -152,7 +152,8 @@
 通知｜つうち
 知名度｜ちめいど
 知人｜ちじん
-知識｜ちしき</t>
+知識｜ちしき
+知能｜ちのう</t>
   </si>
   <si>
     <t>ちまた</t>
@@ -1437,7 +1438,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" ht="90" spans="1:7">
+    <row r="7" ht="108" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
